--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486936_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486936_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.5043</v>
+        <v>5.7745</v>
       </c>
       <c r="E2" t="n">
-        <v>4.1387</v>
+        <v>4.5571</v>
       </c>
       <c r="F2" t="n">
-        <v>1.3657</v>
+        <v>1.2174</v>
       </c>
       <c r="G2" t="n">
         <v>3.8089</v>
@@ -610,13 +610,13 @@
         <v>2.0534</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.4668</v>
+        <v>-0.1966</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.283</v>
+        <v>0.1354</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1838</v>
+        <v>-0.332</v>
       </c>
       <c r="V2" t="n">
         <v>0.1088</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.6097</v>
+        <v>2.5298</v>
       </c>
       <c r="E3" t="n">
-        <v>4.8087</v>
+        <v>3.5806</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.199</v>
+        <v>-1.0507</v>
       </c>
       <c r="G3" t="n">
         <v>-1.0576</v>
@@ -688,13 +688,13 @@
         <v>2.0534</v>
       </c>
       <c r="S3" t="n">
-        <v>1.1951</v>
+        <v>0.1152</v>
       </c>
       <c r="T3" t="n">
-        <v>1.2744</v>
+        <v>0.0463</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0793</v>
+        <v>0.0689</v>
       </c>
       <c r="V3" t="n">
         <v>1.4189</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R. UKAWUBA</t>
+          <t>A. LIBROIA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.686</v>
+        <v>2.2886</v>
       </c>
       <c r="E4" t="n">
-        <v>2.1681</v>
+        <v>1.3563</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.4821</v>
+        <v>0.9322</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9384</v>
+        <v>3.3888</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.7008</v>
+        <v>-0.9367</v>
       </c>
       <c r="I4" t="n">
-        <v>1.6392</v>
+        <v>4.3255</v>
       </c>
       <c r="J4" t="n">
-        <v>1.7615</v>
+        <v>4.2089</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.6195000000000001</v>
+        <v>-0.5795</v>
       </c>
       <c r="L4" t="n">
-        <v>2.381</v>
+        <v>4.7884</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.8231000000000001</v>
+        <v>-0.8201000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.0813</v>
+        <v>-0.3572</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.7418</v>
+        <v>-0.4629</v>
       </c>
       <c r="P4" t="n">
-        <v>1.8481</v>
+        <v>-0.616</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-2.0534</v>
       </c>
       <c r="R4" t="n">
-        <v>1.8481</v>
+        <v>1.4374</v>
       </c>
       <c r="S4" t="n">
-        <v>0.07820000000000001</v>
+        <v>0.214</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4066</v>
+        <v>-0.1009</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3285</v>
+        <v>0.3149</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.1786</v>
+        <v>-0.6982</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>-0.6982</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.1786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. LIBROIA</t>
+          <t>R. UKAWUBA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3984</v>
+        <v>1.354</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9108000000000001</v>
+        <v>1.7768</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4876</v>
+        <v>-0.4228</v>
       </c>
       <c r="G5" t="n">
-        <v>3.3888</v>
+        <v>0.9384</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.9367</v>
+        <v>-0.7008</v>
       </c>
       <c r="I5" t="n">
-        <v>4.3255</v>
+        <v>1.6392</v>
       </c>
       <c r="J5" t="n">
-        <v>4.2089</v>
+        <v>1.7615</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.5795</v>
+        <v>-0.6195000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>4.7884</v>
+        <v>2.381</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.8201000000000001</v>
+        <v>-0.8231000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3572</v>
+        <v>-0.0813</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4629</v>
+        <v>-0.7418</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.616</v>
+        <v>1.8481</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.0534</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.4374</v>
+        <v>1.8481</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.6762</v>
+        <v>-0.2538</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5465</v>
+        <v>0.0154</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1297</v>
+        <v>-0.2692</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.6982</v>
+        <v>-1.1786</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.6982</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0134</v>
+        <v>0.1207</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2333</v>
+        <v>-0.1851</v>
       </c>
       <c r="F6" t="n">
-        <v>0.78</v>
+        <v>0.3058</v>
       </c>
       <c r="G6" t="n">
         <v>-2.7159</v>
@@ -922,13 +922,13 @@
         <v>2.2588</v>
       </c>
       <c r="S6" t="n">
-        <v>1.4274</v>
+        <v>0.5347</v>
       </c>
       <c r="T6" t="n">
-        <v>1.3093</v>
+        <v>0.8909</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1181</v>
+        <v>-0.3562</v>
       </c>
       <c r="V6" t="n">
         <v>1.0698</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. IKPEZE</t>
+          <t>M. VORONIN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5261</v>
+        <v>-0.4566</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2937</v>
+        <v>-2.4176</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.8198</v>
+        <v>1.961</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.9472</v>
+        <v>-4.2534</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.8262</v>
+        <v>-0.0616</v>
       </c>
       <c r="I7" t="n">
-        <v>0.879</v>
+        <v>-4.1918</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.2529</v>
+        <v>-4.0494</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.4108</v>
+        <v>0.5164</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1579</v>
+        <v>-4.5657</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3057</v>
+        <v>-0.204</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4154</v>
+        <v>-0.578</v>
       </c>
       <c r="O7" t="n">
-        <v>0.7211</v>
+        <v>0.374</v>
       </c>
       <c r="P7" t="n">
-        <v>1.6427</v>
+        <v>2.8748</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.6427</v>
+        <v>2.8748</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3921</v>
+        <v>-0.4969</v>
       </c>
       <c r="T7" t="n">
-        <v>0.368</v>
+        <v>0.2129</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.7601</v>
+        <v>-0.7098</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.8295</v>
+        <v>1.4189</v>
       </c>
       <c r="W7" t="n">
-        <v>1.1786</v>
+        <v>1.4189</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.0082</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. PRIOR RUIZ</t>
+          <t>A. IKPEZE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.0147</v>
+        <v>-0.5854</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.0249</v>
+        <v>0.2937</v>
       </c>
       <c r="F8" t="n">
-        <v>2.0102</v>
+        <v>-0.8791</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.8427</v>
+        <v>-0.9472</v>
       </c>
       <c r="H8" t="n">
-        <v>1.2651</v>
+        <v>-1.8262</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.1078</v>
+        <v>0.879</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.5567</v>
+        <v>-1.2529</v>
       </c>
       <c r="K8" t="n">
-        <v>1.4828</v>
+        <v>-1.4108</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.0396</v>
+        <v>0.1579</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.286</v>
+        <v>0.3057</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2177</v>
+        <v>-0.4154</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0682</v>
+        <v>0.7211</v>
       </c>
       <c r="P8" t="n">
-        <v>0.8214</v>
+        <v>1.6427</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.8481</v>
+        <v>1.6427</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5129</v>
+        <v>-0.4513</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.4415</v>
+        <v>0.368</v>
       </c>
       <c r="U8" t="n">
-        <v>0.9285</v>
+        <v>-0.8193</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.4805</v>
+        <v>-0.8295</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.1786</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.4805</v>
+        <v>-2.0082</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. LLORACH CORNELLES</t>
+          <t>A. PRIOR RUIZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.1008</v>
+        <v>-0.6703</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1317</v>
+        <v>-2.2655</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.969</v>
+        <v>1.5952</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.4498</v>
+        <v>-0.8427</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.0552</v>
+        <v>1.2651</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3947</v>
+        <v>-2.1078</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>-0.5567</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1.4828</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-2.0396</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.4498</v>
+        <v>-0.286</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0552</v>
+        <v>-0.2177</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.3947</v>
+        <v>-0.0682</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>0.8214</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.0267</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.8481</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4107</v>
+        <v>-0.1685</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1317</v>
+        <v>-0.6821</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2789</v>
+        <v>0.5135999999999999</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.2402</v>
+        <v>-0.4805</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2402</v>
+        <v>-0.4805</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.4082</v>
+        <v>-0.9034</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.7904</v>
+        <v>-2.3448</v>
       </c>
       <c r="F10" t="n">
-        <v>1.3821</v>
+        <v>1.4414</v>
       </c>
       <c r="G10" t="n">
         <v>-1.8963</v>
@@ -1234,13 +1234,13 @@
         <v>3.4908</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0376</v>
+        <v>-0.5328000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2521</v>
+        <v>0.1935</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.7855</v>
+        <v>-0.7262</v>
       </c>
       <c r="V10" t="n">
         <v>-0.9384</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. VORONIN</t>
+          <t>P. LLORACH CORNELLES</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.4696</v>
+        <v>-1.1008</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.0453</v>
+        <v>-0.1317</v>
       </c>
       <c r="F11" t="n">
-        <v>1.5757</v>
+        <v>-0.969</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.2534</v>
+        <v>-0.4498</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.0616</v>
+        <v>-0.0552</v>
       </c>
       <c r="I11" t="n">
-        <v>-4.1918</v>
+        <v>-0.3947</v>
       </c>
       <c r="J11" t="n">
-        <v>-4.0494</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.5164</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>-4.5657</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.204</v>
+        <v>-0.4498</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.578</v>
+        <v>-0.0552</v>
       </c>
       <c r="O11" t="n">
-        <v>0.374</v>
+        <v>-0.3947</v>
       </c>
       <c r="P11" t="n">
-        <v>2.8748</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.8748</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.5099</v>
+        <v>-0.4107</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4147</v>
+        <v>-0.1317</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.0951</v>
+        <v>-0.2789</v>
       </c>
       <c r="V11" t="n">
-        <v>1.4189</v>
+        <v>-0.2402</v>
       </c>
       <c r="W11" t="n">
-        <v>1.4189</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>7.692400000000003</v>
+        <v>8.351100000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>3.560999999999999</v>
+        <v>4.219800000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>4.1314</v>
+        <v>4.131399999999999</v>
       </c>
       <c r="G12" t="n">
         <v>-4.026800000000001</v>
@@ -1363,13 +1363,13 @@
         <v>1.973300000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>2.227399999999999</v>
+        <v>2.2274</v>
       </c>
       <c r="K12" t="n">
         <v>-2.9799</v>
       </c>
       <c r="L12" t="n">
-        <v>5.2074</v>
+        <v>5.207399999999999</v>
       </c>
       <c r="M12" t="n">
         <v>-6.2543</v>
@@ -1390,16 +1390,16 @@
         <v>19.5075</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.3055</v>
+        <v>-1.6467</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2888</v>
+        <v>0.9477000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.5943</v>
+        <v>-2.5942</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.349</v>
+        <v>-0.3490000000000001</v>
       </c>
       <c r="W12" t="n">
         <v>6.1783</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>P. ASO JIMENEZ</t>
+          <t>O. ALVARADO RODRIGUEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.7416</v>
+        <v>3.8343</v>
       </c>
       <c r="E13" t="n">
-        <v>0.8953</v>
+        <v>3.6535</v>
       </c>
       <c r="F13" t="n">
-        <v>2.8462</v>
+        <v>0.1808</v>
       </c>
       <c r="G13" t="n">
-        <v>1.8985</v>
+        <v>4.3089</v>
       </c>
       <c r="H13" t="n">
-        <v>0.7038</v>
+        <v>1.0409</v>
       </c>
       <c r="I13" t="n">
-        <v>1.1947</v>
+        <v>3.268</v>
       </c>
       <c r="J13" t="n">
-        <v>0.6823</v>
+        <v>4.7734</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.5806</v>
+        <v>1.0901</v>
       </c>
       <c r="L13" t="n">
-        <v>1.2629</v>
+        <v>3.6834</v>
       </c>
       <c r="M13" t="n">
-        <v>1.2161</v>
+        <v>-0.4645</v>
       </c>
       <c r="N13" t="n">
-        <v>1.2843</v>
+        <v>-0.0492</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.0682</v>
+        <v>-0.4154</v>
       </c>
       <c r="P13" t="n">
-        <v>0.2053</v>
+        <v>-0.616</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-1.2321</v>
       </c>
       <c r="R13" t="n">
-        <v>0.2053</v>
+        <v>0.616</v>
       </c>
       <c r="S13" t="n">
-        <v>0.6994</v>
+        <v>0.1414</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0272</v>
+        <v>0.1121</v>
       </c>
       <c r="U13" t="n">
-        <v>0.7266</v>
+        <v>0.0293</v>
       </c>
       <c r="V13" t="n">
-        <v>0.9384</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>0.2402</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0.6982</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>O. ALVARADO RODRIGUEZ</t>
+          <t>P. ASO JIMENEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.2031</v>
+        <v>3.6282</v>
       </c>
       <c r="E14" t="n">
-        <v>3.3397</v>
+        <v>0.7907</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.1366</v>
+        <v>2.8375</v>
       </c>
       <c r="G14" t="n">
-        <v>4.3089</v>
+        <v>1.8985</v>
       </c>
       <c r="H14" t="n">
-        <v>1.0409</v>
+        <v>0.7038</v>
       </c>
       <c r="I14" t="n">
-        <v>3.268</v>
+        <v>1.1947</v>
       </c>
       <c r="J14" t="n">
-        <v>4.7734</v>
+        <v>0.6823</v>
       </c>
       <c r="K14" t="n">
-        <v>1.0901</v>
+        <v>-0.5806</v>
       </c>
       <c r="L14" t="n">
-        <v>3.6834</v>
+        <v>1.2629</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.4645</v>
+        <v>1.2161</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.0492</v>
+        <v>1.2843</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.4154</v>
+        <v>-0.0682</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.616</v>
+        <v>0.2053</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.2321</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.616</v>
+        <v>0.2053</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.4897</v>
+        <v>0.586</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2017</v>
+        <v>-0.1318</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2881</v>
+        <v>0.7179</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.9384</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>0.2402</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>0.6982</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9886</v>
+        <v>1.7191</v>
       </c>
       <c r="E15" t="n">
-        <v>0.144</v>
+        <v>0.6671</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8446</v>
+        <v>1.0521</v>
       </c>
       <c r="G15" t="n">
         <v>2.2296</v>
@@ -1624,13 +1624,13 @@
         <v>0.2053</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.4196</v>
+        <v>0.311</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2558</v>
+        <v>0.2673</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1638</v>
+        <v>0.0437</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>E. GATELL SANZ</t>
+          <t>A. ARAGONES NAVAIS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2898</v>
+        <v>-0.1517</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0873</v>
+        <v>-1.1787</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.3771</v>
+        <v>1.027</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6494</v>
+        <v>-1.8792</v>
       </c>
       <c r="H16" t="n">
-        <v>1.9594</v>
+        <v>-0.24</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.31</v>
+        <v>-1.6392</v>
       </c>
       <c r="J16" t="n">
-        <v>1.1454</v>
+        <v>-2.3956</v>
       </c>
       <c r="K16" t="n">
-        <v>1.6454</v>
+        <v>-1.0798</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.5</v>
+        <v>-1.3158</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.496</v>
+        <v>0.5164</v>
       </c>
       <c r="N16" t="n">
-        <v>0.314</v>
+        <v>0.8398</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.3234</v>
       </c>
       <c r="P16" t="n">
-        <v>-2.2588</v>
+        <v>0.2053</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.0801</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.8214</v>
+        <v>0.2053</v>
       </c>
       <c r="S16" t="n">
-        <v>2.7385</v>
+        <v>0.2122</v>
       </c>
       <c r="T16" t="n">
-        <v>2.0221</v>
+        <v>-0.3333</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7164</v>
+        <v>0.5455</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.4189</v>
+        <v>1.31</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.5503</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.4189</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.7255</v>
+        <v>-0.2426</v>
       </c>
       <c r="E17" t="n">
-        <v>-3.2561</v>
+        <v>-2.9423</v>
       </c>
       <c r="F17" t="n">
-        <v>2.5305</v>
+        <v>2.6997</v>
       </c>
       <c r="G17" t="n">
         <v>3.0623</v>
@@ -1780,13 +1780,13 @@
         <v>0.616</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0034</v>
+        <v>0.4795</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3566</v>
+        <v>-0.0428</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3532</v>
+        <v>0.5223</v>
       </c>
       <c r="V17" t="n">
         <v>0.9384</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. ARAGONES NAVAIS</t>
+          <t>E. GATELL SANZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.8438</v>
+        <v>-2.1623</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.7017</v>
+        <v>-1.2725</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8579</v>
+        <v>-0.8898</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.8792</v>
+        <v>0.6494</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.24</v>
+        <v>1.9594</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.6392</v>
+        <v>-1.31</v>
       </c>
       <c r="J18" t="n">
-        <v>-2.3956</v>
+        <v>1.1454</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.0798</v>
+        <v>1.6454</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.3158</v>
+        <v>-0.5</v>
       </c>
       <c r="M18" t="n">
-        <v>0.5164</v>
+        <v>-0.496</v>
       </c>
       <c r="N18" t="n">
-        <v>0.8398</v>
+        <v>0.314</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.3234</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="P18" t="n">
-        <v>0.2053</v>
+        <v>-2.2588</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-3.0801</v>
       </c>
       <c r="R18" t="n">
-        <v>0.2053</v>
+        <v>0.8214</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.48</v>
+        <v>0.866</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8563</v>
+        <v>0.6623</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3764</v>
+        <v>0.2037</v>
       </c>
       <c r="V18" t="n">
-        <v>1.31</v>
+        <v>-1.4189</v>
       </c>
       <c r="W18" t="n">
-        <v>1.5503</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2402</v>
+        <v>-1.4189</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. MUÑOZ SAMATAN</t>
+          <t>Y. KOLO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.3622</v>
+        <v>-2.3803</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3202</v>
+        <v>-1.0019</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.6824</v>
+        <v>-1.3783</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.1005</v>
+        <v>-1.4008</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.1192</v>
+        <v>0.107</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.9813</v>
+        <v>-1.5077</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.4389</v>
+        <v>-1.3118</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.5703</v>
+        <v>-0.0355</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1314</v>
+        <v>-1.2763</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.6616</v>
+        <v>-0.089</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.5489000000000001</v>
+        <v>0.1425</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.1127</v>
+        <v>-0.2314</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.4374</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.2588</v>
+        <v>-0.2053</v>
       </c>
       <c r="R19" t="n">
-        <v>0.8214</v>
+        <v>0.2053</v>
       </c>
       <c r="S19" t="n">
-        <v>1.765</v>
+        <v>0.5482</v>
       </c>
       <c r="T19" t="n">
-        <v>2.7776</v>
+        <v>0.275</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.0126</v>
+        <v>0.2732</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.5893</v>
+        <v>-1.5277</v>
       </c>
       <c r="W19" t="n">
         <v>0.2402</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.8295</v>
+        <v>-1.7679</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Y. KOLO</t>
+          <t>D. MUÑOZ SAMATAN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.4256</v>
+        <v>-3.5616</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.1066</v>
+        <v>-1.3534</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.319</v>
+        <v>-2.2081</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.4008</v>
+        <v>-2.1005</v>
       </c>
       <c r="H20" t="n">
-        <v>0.107</v>
+        <v>-1.1192</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.5077</v>
+        <v>-0.9813</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.3118</v>
+        <v>-0.4389</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.0355</v>
+        <v>-0.5703</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.2763</v>
+        <v>0.1314</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.089</v>
+        <v>-1.6616</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1425</v>
+        <v>-0.5489000000000001</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2314</v>
+        <v>-1.1127</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>-1.4374</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.2053</v>
+        <v>-2.2588</v>
       </c>
       <c r="R20" t="n">
-        <v>0.2053</v>
+        <v>0.8214</v>
       </c>
       <c r="S20" t="n">
-        <v>0.5029</v>
+        <v>0.5656</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1704</v>
+        <v>1.104</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3325</v>
+        <v>-0.5384</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.5277</v>
+        <v>-0.5893</v>
       </c>
       <c r="W20" t="n">
         <v>0.2402</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.7679</v>
+        <v>-0.8295</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.2519</v>
+        <v>-3.8021</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.7025</v>
+        <v>-0.07480000000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.5494</v>
+        <v>-3.7273</v>
       </c>
       <c r="G21" t="n">
         <v>0.3694</v>
@@ -2092,13 +2092,13 @@
         <v>0.616</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7732</v>
+        <v>-0.3235</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1744</v>
+        <v>0.4532</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5988</v>
+        <v>-0.7766</v>
       </c>
       <c r="V21" t="n">
         <v>-1.1786</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.727</v>
+        <v>-3.8762</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.3915</v>
+        <v>-1.6593</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.3355</v>
+        <v>-2.2169</v>
       </c>
       <c r="G22" t="n">
         <v>-3.1107</v>
@@ -2170,13 +2170,13 @@
         <v>0.8214</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.2343</v>
+        <v>-0.3835</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5038</v>
+        <v>0.2284</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.7305</v>
+        <v>-0.612</v>
       </c>
       <c r="V22" t="n">
         <v>1.8768</v>
@@ -2203,16 +2203,16 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.692500000000001</v>
+        <v>-6.995199999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.371899999999999</v>
+        <v>-4.3716</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.3208</v>
+        <v>-2.6233</v>
       </c>
       <c r="G23" t="n">
-        <v>4.026900000000001</v>
+        <v>4.026899999999999</v>
       </c>
       <c r="H23" t="n">
         <v>6.0002</v>
@@ -2245,25 +2245,25 @@
         <v>-19.5075</v>
       </c>
       <c r="R23" t="n">
-        <v>5.133399999999999</v>
+        <v>5.1334</v>
       </c>
       <c r="S23" t="n">
-        <v>2.3056</v>
+        <v>3.002899999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>2.5943</v>
+        <v>2.5944</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2887000000000001</v>
+        <v>0.4085999999999997</v>
       </c>
       <c r="V23" t="n">
-        <v>0.3491000000000002</v>
+        <v>0.3491</v>
       </c>
       <c r="W23" t="n">
         <v>6.2873</v>
       </c>
       <c r="X23" t="n">
-        <v>-5.9382</v>
+        <v>-5.938199999999999</v>
       </c>
     </row>
   </sheetData>
